--- a/data/nzd0134/nzd0134.xlsx
+++ b/data/nzd0134/nzd0134.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F651"/>
+  <dimension ref="A1:F656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16042,6 +16042,126 @@
         <v>370.14</v>
       </c>
       <c r="F651" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>381.39</v>
+      </c>
+      <c r="C652" t="n">
+        <v>375.95</v>
+      </c>
+      <c r="D652" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="E652" t="n">
+        <v>369.82</v>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>382.16</v>
+      </c>
+      <c r="C653" t="n">
+        <v>374.59</v>
+      </c>
+      <c r="D653" t="n">
+        <v>381.15</v>
+      </c>
+      <c r="E653" t="n">
+        <v>368.96</v>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="C654" t="n">
+        <v>374.29</v>
+      </c>
+      <c r="D654" t="n">
+        <v>381.36</v>
+      </c>
+      <c r="E654" t="n">
+        <v>368.76</v>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>382.1</v>
+      </c>
+      <c r="C655" t="n">
+        <v>374.37</v>
+      </c>
+      <c r="D655" t="n">
+        <v>381.78</v>
+      </c>
+      <c r="E655" t="n">
+        <v>368.95</v>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>381.73</v>
+      </c>
+      <c r="C656" t="n">
+        <v>374.42</v>
+      </c>
+      <c r="D656" t="n">
+        <v>381.88</v>
+      </c>
+      <c r="E656" t="n">
+        <v>369.29</v>
+      </c>
+      <c r="F656" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16058,7 +16178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B704"/>
+  <dimension ref="A1:B709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23101,6 +23221,56 @@
       </c>
       <c r="B704" t="n">
         <v>-0.86</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -23269,28 +23439,28 @@
         <v>0.0522</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1198303190031456</v>
+        <v>-0.110863958575913</v>
       </c>
       <c r="J2" t="n">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="K2" t="n">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04453289207065014</v>
+        <v>0.03843293992288865</v>
       </c>
       <c r="M2" t="n">
-        <v>3.194510223283073</v>
+        <v>3.215264768670939</v>
       </c>
       <c r="N2" t="n">
-        <v>17.68628897634122</v>
+        <v>17.8208104015067</v>
       </c>
       <c r="O2" t="n">
-        <v>4.205506982082092</v>
+        <v>4.221470170628558</v>
       </c>
       <c r="P2" t="n">
-        <v>379.201352377705</v>
+        <v>379.1076013681374</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23347,28 +23517,28 @@
         <v>0.1245</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01003334984085291</v>
+        <v>0.01152615796457686</v>
       </c>
       <c r="J3" t="n">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="K3" t="n">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000926553112779116</v>
+        <v>0.001241460828569907</v>
       </c>
       <c r="M3" t="n">
-        <v>2.055582637596982</v>
+        <v>2.047186961969795</v>
       </c>
       <c r="N3" t="n">
-        <v>6.22312890890709</v>
+        <v>6.185830350379198</v>
       </c>
       <c r="O3" t="n">
-        <v>2.494619992886109</v>
+        <v>2.48713295792147</v>
       </c>
       <c r="P3" t="n">
-        <v>373.4581792562039</v>
+        <v>373.442569592558</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23425,28 +23595,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07718449797516652</v>
+        <v>-0.07508543571945639</v>
       </c>
       <c r="J4" t="n">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="K4" t="n">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0348683806266854</v>
+        <v>0.03355969980396079</v>
       </c>
       <c r="M4" t="n">
-        <v>2.428096255207484</v>
+        <v>2.420159950620317</v>
       </c>
       <c r="N4" t="n">
-        <v>9.428842615109927</v>
+        <v>9.37221203431946</v>
       </c>
       <c r="O4" t="n">
-        <v>3.070642052586059</v>
+        <v>3.061406871737153</v>
       </c>
       <c r="P4" t="n">
-        <v>382.3029784475394</v>
+        <v>382.2810025841861</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23503,28 +23673,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1624974251413243</v>
+        <v>-0.1627485747091616</v>
       </c>
       <c r="J5" t="n">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="K5" t="n">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1593818618615848</v>
+        <v>0.1620965144292696</v>
       </c>
       <c r="M5" t="n">
-        <v>2.244039239476702</v>
+        <v>2.229524294682549</v>
       </c>
       <c r="N5" t="n">
-        <v>7.95295678320087</v>
+        <v>7.893509460566289</v>
       </c>
       <c r="O5" t="n">
-        <v>2.820098718697782</v>
+        <v>2.809539012109689</v>
       </c>
       <c r="P5" t="n">
-        <v>373.6910601533392</v>
+        <v>373.6936909429531</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23562,7 +23732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F651"/>
+  <dimension ref="A1:F656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44365,6 +44535,166 @@
         </is>
       </c>
     </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>-36.55171631860166,174.70994292549713</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>-36.552435964706525,174.70991157491656</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>-36.5531324415243,174.7100545135098</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>-36.553848409898976,174.71011976737785</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>-36.55171600863424,174.70995151819773</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>-36.55243684751736,174.70989642235162</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>-36.55313369344082,174.71004537259503</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>-36.553850228241316,174.71011042859814</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>-36.551715871765325,174.70995531237716</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>-36.55243704225477,174.70989307987398</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>-36.55313337669093,174.71004768535664</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>-36.55385065111153,174.71010825678883</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>-36.55171603278758,174.70995084863665</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>-36.55243699032479,174.70989397120135</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>-36.553132743191,174.71005231087975</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>-36.55385024938482,174.71011032000766</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>-36.55171618173301,174.70994671967665</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>-36.55243695786857,174.70989452828096</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>-36.55313259235765,174.71005341219478</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>-36.55384953050539,174.71011401208344</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0134/nzd0134.xlsx
+++ b/data/nzd0134/nzd0134.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F656"/>
+  <dimension ref="A1:F659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16162,6 +16162,78 @@
         <v>369.29</v>
       </c>
       <c r="F656" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>382.11</v>
+      </c>
+      <c r="C657" t="n">
+        <v>374.72</v>
+      </c>
+      <c r="D657" t="n">
+        <v>382.47</v>
+      </c>
+      <c r="E657" t="n">
+        <v>369.92</v>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>382.91</v>
+      </c>
+      <c r="C658" t="n">
+        <v>374.62</v>
+      </c>
+      <c r="D658" t="n">
+        <v>382.61</v>
+      </c>
+      <c r="E658" t="n">
+        <v>370.44</v>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>382.91</v>
+      </c>
+      <c r="C659" t="n">
+        <v>374.62</v>
+      </c>
+      <c r="D659" t="n">
+        <v>382.61</v>
+      </c>
+      <c r="E659" t="n">
+        <v>370.42</v>
+      </c>
+      <c r="F659" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16178,7 +16250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B709"/>
+  <dimension ref="A1:B712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23271,6 +23343,36 @@
       </c>
       <c r="B709" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23439,28 +23541,28 @@
         <v>0.0522</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.110863958575913</v>
+        <v>-0.1050394472815329</v>
       </c>
       <c r="J2" t="n">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="K2" t="n">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03843293992288865</v>
+        <v>0.03461611254488528</v>
       </c>
       <c r="M2" t="n">
-        <v>3.215264768670939</v>
+        <v>3.231101915372103</v>
       </c>
       <c r="N2" t="n">
-        <v>17.8208104015067</v>
+        <v>17.93228986093639</v>
       </c>
       <c r="O2" t="n">
-        <v>4.221470170628558</v>
+        <v>4.23465345228348</v>
       </c>
       <c r="P2" t="n">
-        <v>379.1076013681374</v>
+        <v>379.046428139523</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23517,28 +23619,28 @@
         <v>0.1245</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01152615796457686</v>
+        <v>0.01232915510884898</v>
       </c>
       <c r="J3" t="n">
+        <v>658</v>
+      </c>
+      <c r="K3" t="n">
         <v>655</v>
       </c>
-      <c r="K3" t="n">
-        <v>652</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.001241460828569907</v>
+        <v>0.001433923686781413</v>
       </c>
       <c r="M3" t="n">
-        <v>2.047186961969795</v>
+        <v>2.041766140404435</v>
       </c>
       <c r="N3" t="n">
-        <v>6.185830350379198</v>
+        <v>6.161164027337784</v>
       </c>
       <c r="O3" t="n">
-        <v>2.48713295792147</v>
+        <v>2.482169218111002</v>
       </c>
       <c r="P3" t="n">
-        <v>373.442569592558</v>
+        <v>373.4341335944261</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23595,28 +23697,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07508543571945639</v>
+        <v>-0.07302413135363144</v>
       </c>
       <c r="J4" t="n">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="K4" t="n">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03355969980396079</v>
+        <v>0.03203684570443999</v>
       </c>
       <c r="M4" t="n">
-        <v>2.420159950620317</v>
+        <v>2.41968630182756</v>
       </c>
       <c r="N4" t="n">
-        <v>9.37221203431946</v>
+        <v>9.35342605521434</v>
       </c>
       <c r="O4" t="n">
-        <v>3.061406871737153</v>
+        <v>3.058337138906425</v>
       </c>
       <c r="P4" t="n">
-        <v>382.2810025841861</v>
+        <v>382.2593285258296</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23673,28 +23775,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1627485747091616</v>
+        <v>-0.1618953909047521</v>
       </c>
       <c r="J5" t="n">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="K5" t="n">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1620965144292696</v>
+        <v>0.1619834881409344</v>
       </c>
       <c r="M5" t="n">
-        <v>2.229524294682549</v>
+        <v>2.224189255968824</v>
       </c>
       <c r="N5" t="n">
-        <v>7.893509460566289</v>
+        <v>7.861888959398074</v>
       </c>
       <c r="O5" t="n">
-        <v>2.809539012109689</v>
+        <v>2.803906018289143</v>
       </c>
       <c r="P5" t="n">
-        <v>373.6936909429531</v>
+        <v>373.6847144619095</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23732,7 +23834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F656"/>
+  <dimension ref="A1:F659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44695,6 +44797,102 @@
         </is>
       </c>
     </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>-36.551716028762016,174.70995096023015</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>-36.552436763131105,174.70989787075857</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>-36.55313170244072,174.71005990995332</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>-36.55384819846376,174.71012085328246</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>-36.55171570671732,174.70995988771116</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>-36.5524368280436,174.70989675659936</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>-36.55313149127394,174.7100614517943</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>-36.55384709900055,174.71012649998622</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>-36.55171570671732,174.70995988771116</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>-36.5524368280436,174.70989675659936</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>-36.55313149127394,174.7100614517943</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>-36.553847141287605,174.7101262828053</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0134/nzd0134.xlsx
+++ b/data/nzd0134/nzd0134.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F659"/>
+  <dimension ref="A1:F660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16234,6 +16234,30 @@
         <v>370.42</v>
       </c>
       <c r="F659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>383.05</v>
+      </c>
+      <c r="C660" t="n">
+        <v>374.99</v>
+      </c>
+      <c r="D660" t="n">
+        <v>382.75</v>
+      </c>
+      <c r="E660" t="n">
+        <v>370.52</v>
+      </c>
+      <c r="F660" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16250,7 +16274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B712"/>
+  <dimension ref="A1:B713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23373,6 +23397,16 @@
       </c>
       <c r="B712" t="n">
         <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -23541,28 +23575,28 @@
         <v>0.0522</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1050394472815329</v>
+        <v>-0.103001488048443</v>
       </c>
       <c r="J2" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K2" t="n">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03461611254488528</v>
+        <v>0.03331222682163193</v>
       </c>
       <c r="M2" t="n">
-        <v>3.231101915372103</v>
+        <v>3.236941998377317</v>
       </c>
       <c r="N2" t="n">
-        <v>17.93228986093639</v>
+        <v>17.97602405347462</v>
       </c>
       <c r="O2" t="n">
-        <v>4.23465345228348</v>
+        <v>4.239814153176366</v>
       </c>
       <c r="P2" t="n">
-        <v>379.046428139523</v>
+        <v>379.0249574907975</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -23619,28 +23653,28 @@
         <v>0.1245</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01232915510884898</v>
+        <v>0.01269316756256505</v>
       </c>
       <c r="J3" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K3" t="n">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001433923686781413</v>
+        <v>0.001524332108955639</v>
       </c>
       <c r="M3" t="n">
-        <v>2.041766140404435</v>
+        <v>2.040443617295663</v>
       </c>
       <c r="N3" t="n">
-        <v>6.161164027337784</v>
+        <v>6.1540365253344</v>
       </c>
       <c r="O3" t="n">
-        <v>2.482169218111002</v>
+        <v>2.480733062087576</v>
       </c>
       <c r="P3" t="n">
-        <v>373.4341335944261</v>
+        <v>373.4302970877256</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -23697,28 +23731,28 @@
         <v>0.07829999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07302413135363144</v>
+        <v>-0.07228766764571859</v>
       </c>
       <c r="J4" t="n">
+        <v>659</v>
+      </c>
+      <c r="K4" t="n">
         <v>658</v>
       </c>
-      <c r="K4" t="n">
-        <v>657</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.03203684570443999</v>
+        <v>0.03148787698975586</v>
       </c>
       <c r="M4" t="n">
-        <v>2.41968630182756</v>
+        <v>2.419790033040515</v>
       </c>
       <c r="N4" t="n">
-        <v>9.35342605521434</v>
+        <v>9.34844615397523</v>
       </c>
       <c r="O4" t="n">
-        <v>3.058337138906425</v>
+        <v>3.057522878732918</v>
       </c>
       <c r="P4" t="n">
-        <v>382.2593285258296</v>
+        <v>382.2515606886209</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -23775,28 +23809,28 @@
         <v>0.0798</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1618953909047521</v>
+        <v>-0.1615336632387777</v>
       </c>
       <c r="J5" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K5" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1619834881409344</v>
+        <v>0.1618010198983781</v>
       </c>
       <c r="M5" t="n">
-        <v>2.224189255968824</v>
+        <v>2.222847629388213</v>
       </c>
       <c r="N5" t="n">
-        <v>7.861888959398074</v>
+        <v>7.852182748884436</v>
       </c>
       <c r="O5" t="n">
-        <v>2.803906018289143</v>
+        <v>2.802174646392412</v>
       </c>
       <c r="P5" t="n">
-        <v>373.6847144619095</v>
+        <v>373.6808977488476</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -23834,7 +23868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F659"/>
+  <dimension ref="A1:F660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44893,6 +44927,38 @@
         </is>
       </c>
     </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>-36.55171565035944,174.70996145002033</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>-36.552436587867305,174.7099008789884</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>-36.55313128010715,174.71006299363526</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>-36.55384692985234,174.71012736870986</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
